--- a/reports/20260507/API_Admit_Card_Cases_claude.xlsx
+++ b/reports/20260507/API_Admit_Card_Cases_claude.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>status=KO, FilePath=missing, error={'description': 'Unable to form admit card'}</t>
+          <t>status=KO, FilePath=present, error=None</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>status=KO, previewUrl=missing, error={'description': 'Unable to form admit card'}</t>
+          <t>status=OK, previewUrl=present, error=None</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>status=None, xss_reflected=False</t>
+          <t>status=OK, xss_reflected=False</t>
         </is>
       </c>
     </row>
